--- a/Daily_Report/Top 7 broker List with its Turnover 2024-07-23.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-07-23.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="285">
   <si>
     <t>Date: 2024-07-23</t>
   </si>
@@ -59,106 +59,109 @@
     <t>7</t>
   </si>
   <si>
+    <t>Naasa Securities Co. Ltd.</t>
+  </si>
+  <si>
+    <t>Imperial Securities Co .Pvt.Limited</t>
+  </si>
+  <si>
+    <t>Vision Securities Pvt.Limited</t>
+  </si>
+  <si>
+    <t>Online Securities Pvt.Ltd</t>
+  </si>
+  <si>
+    <t>Sani Securities Company Limited</t>
+  </si>
+  <si>
     <t>Dynamic Money Managers Securities Pvt.Ltd</t>
   </si>
   <si>
-    <t>Linch Stock Market Limited</t>
-  </si>
-  <si>
-    <t>Agrawal Securities Pvt. Limited</t>
-  </si>
-  <si>
-    <t>Naasa Securities Co. Ltd.</t>
-  </si>
-  <si>
-    <t>Imperial Securities Co .Pvt.Limited</t>
-  </si>
-  <si>
-    <t>Online Securities Pvt.Ltd</t>
-  </si>
-  <si>
-    <t>Sani Securities Company Limited</t>
+    <t>ABC Securities Pvt. Limited</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>42</t>
   </si>
   <si>
     <t>44</t>
   </si>
   <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>8,288,707,585.88</t>
-  </si>
-  <si>
-    <t>2,883,639,127.2</t>
-  </si>
-  <si>
-    <t>1,825,750,576.17</t>
-  </si>
-  <si>
-    <t>1,505,649,520.19</t>
-  </si>
-  <si>
-    <t>1,274,731,902.19</t>
-  </si>
-  <si>
-    <t>1,150,550,279.8</t>
-  </si>
-  <si>
-    <t>1,040,964,394.25</t>
-  </si>
-  <si>
-    <t>4,969,971,231.4</t>
-  </si>
-  <si>
-    <t>2,691,017,364.6</t>
-  </si>
-  <si>
-    <t>910,069,144.01</t>
-  </si>
-  <si>
-    <t>802,126,214.9</t>
-  </si>
-  <si>
-    <t>503,059,566.14</t>
-  </si>
-  <si>
-    <t>376,414,673.8</t>
-  </si>
-  <si>
-    <t>587,571,710.75</t>
-  </si>
-  <si>
-    <t>3,318,736,354.48</t>
-  </si>
-  <si>
-    <t>192,621,762.6</t>
-  </si>
-  <si>
-    <t>915,681,432.16</t>
-  </si>
-  <si>
-    <t>703,523,305.3</t>
-  </si>
-  <si>
-    <t>771,672,336.05</t>
-  </si>
-  <si>
-    <t>774,135,606.0</t>
-  </si>
-  <si>
-    <t>453,392,683.5</t>
+    <t>17</t>
+  </si>
+  <si>
+    <t>1,568,316,975.07</t>
+  </si>
+  <si>
+    <t>1,192,823,985.58</t>
+  </si>
+  <si>
+    <t>1,141,078,238.98</t>
+  </si>
+  <si>
+    <t>975,639,548.9</t>
+  </si>
+  <si>
+    <t>958,214,385.75</t>
+  </si>
+  <si>
+    <t>895,499,956.38</t>
+  </si>
+  <si>
+    <t>843,058,496.85</t>
+  </si>
+  <si>
+    <t>897,496,384.0</t>
+  </si>
+  <si>
+    <t>553,313,475.84</t>
+  </si>
+  <si>
+    <t>634,128,721.58</t>
+  </si>
+  <si>
+    <t>576,063,976.29</t>
+  </si>
+  <si>
+    <t>480,551,265.45</t>
+  </si>
+  <si>
+    <t>449,024,057.5</t>
+  </si>
+  <si>
+    <t>302,399,216.64</t>
+  </si>
+  <si>
+    <t>670,820,591.07</t>
+  </si>
+  <si>
+    <t>639,510,509.74</t>
+  </si>
+  <si>
+    <t>506,949,517.4</t>
+  </si>
+  <si>
+    <t>399,575,572.6</t>
+  </si>
+  <si>
+    <t>477,663,120.3</t>
+  </si>
+  <si>
+    <t>446,475,898.88</t>
+  </si>
+  <si>
+    <t>540,659,280.2</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -176,343 +179,358 @@
     <t>% of turnover</t>
   </si>
   <si>
+    <t>RHPL</t>
+  </si>
+  <si>
+    <t>70,490,005.7</t>
+  </si>
+  <si>
+    <t>NRN</t>
+  </si>
+  <si>
+    <t>64,094,665.8</t>
+  </si>
+  <si>
+    <t>NGPL</t>
+  </si>
+  <si>
+    <t>46,556,192.9</t>
+  </si>
+  <si>
+    <t>PHCL</t>
+  </si>
+  <si>
+    <t>43,404,313.5</t>
+  </si>
+  <si>
+    <t>SHINE</t>
+  </si>
+  <si>
+    <t>33,531,840.8</t>
+  </si>
+  <si>
+    <t>MEN</t>
+  </si>
+  <si>
+    <t>30,118,819.6</t>
+  </si>
+  <si>
+    <t>HRL</t>
+  </si>
+  <si>
+    <t>17,683,787.0</t>
+  </si>
+  <si>
+    <t>GCIL</t>
+  </si>
+  <si>
+    <t>16,557,764.4</t>
+  </si>
+  <si>
+    <t>CIT</t>
+  </si>
+  <si>
+    <t>14,655,939.6</t>
+  </si>
+  <si>
+    <t>NLIC</t>
+  </si>
+  <si>
+    <t>12,231,133.5</t>
+  </si>
+  <si>
+    <t>SADBL</t>
+  </si>
+  <si>
+    <t>22,837,001.3</t>
+  </si>
+  <si>
+    <t>HDHPC</t>
+  </si>
+  <si>
+    <t>18,358,570.89</t>
+  </si>
+  <si>
+    <t>NICA</t>
+  </si>
+  <si>
+    <t>18,112,569.7</t>
+  </si>
+  <si>
+    <t>SHIVM</t>
+  </si>
+  <si>
+    <t>14,899,257.5</t>
+  </si>
+  <si>
+    <t>NLICL</t>
+  </si>
+  <si>
+    <t>13,532,961.1</t>
+  </si>
+  <si>
+    <t>LSL</t>
+  </si>
+  <si>
+    <t>95,452,672.9</t>
+  </si>
+  <si>
+    <t>STC</t>
+  </si>
+  <si>
+    <t>22,205,160.5</t>
+  </si>
+  <si>
+    <t>CHCL</t>
+  </si>
+  <si>
+    <t>19,703,214.7</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>15,362,710.4</t>
+  </si>
+  <si>
+    <t>SHPC</t>
+  </si>
+  <si>
+    <t>15,237,720.1</t>
+  </si>
+  <si>
+    <t>FMDBL</t>
+  </si>
+  <si>
+    <t>29,947,518.4</t>
+  </si>
+  <si>
+    <t>16,004,556.0</t>
+  </si>
+  <si>
+    <t>UPPER</t>
+  </si>
+  <si>
+    <t>10,572,475.69</t>
+  </si>
+  <si>
+    <t>NMB</t>
+  </si>
+  <si>
+    <t>9,305,977.6</t>
+  </si>
+  <si>
+    <t>GBIME</t>
+  </si>
+  <si>
+    <t>8,623,773.3</t>
+  </si>
+  <si>
     <t>SBI</t>
   </si>
   <si>
-    <t>4,780,052,554.5</t>
-  </si>
-  <si>
-    <t>SHL</t>
-  </si>
-  <si>
-    <t>35,417,975.0</t>
+    <t>76,208,072.3</t>
   </si>
   <si>
     <t>SANIMA</t>
   </si>
   <si>
-    <t>24,197,516.8</t>
-  </si>
-  <si>
-    <t>NLICL</t>
-  </si>
-  <si>
-    <t>15,510,000.0</t>
+    <t>34,569,968.79</t>
+  </si>
+  <si>
+    <t>HLI</t>
+  </si>
+  <si>
+    <t>21,401,862.7</t>
+  </si>
+  <si>
+    <t>MNBBL</t>
+  </si>
+  <si>
+    <t>20,335,645.0</t>
+  </si>
+  <si>
+    <t>SPIL</t>
+  </si>
+  <si>
+    <t>17,032,981.0</t>
+  </si>
+  <si>
+    <t>LICN</t>
+  </si>
+  <si>
+    <t>8,340,850.0</t>
+  </si>
+  <si>
+    <t>AHPC</t>
+  </si>
+  <si>
+    <t>8,150,947.4</t>
+  </si>
+  <si>
+    <t>SBL</t>
+  </si>
+  <si>
+    <t>7,215,002.5</t>
+  </si>
+  <si>
+    <t>HATHY</t>
+  </si>
+  <si>
+    <t>7,199,931.6</t>
+  </si>
+  <si>
+    <t>7,112,809.2</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>GMFBS</t>
+  </si>
+  <si>
+    <t>38,703,313.7</t>
+  </si>
+  <si>
+    <t>19,614,915.3</t>
+  </si>
+  <si>
+    <t>SJCL</t>
+  </si>
+  <si>
+    <t>14,249,558.0</t>
+  </si>
+  <si>
+    <t>13,622,786.1</t>
+  </si>
+  <si>
+    <t>MMKJL</t>
+  </si>
+  <si>
+    <t>12,315,457.0</t>
+  </si>
+  <si>
+    <t>29,479,911.9</t>
+  </si>
+  <si>
+    <t>UMRH</t>
+  </si>
+  <si>
+    <t>28,297,380.3</t>
+  </si>
+  <si>
+    <t>25,298,708.0</t>
+  </si>
+  <si>
+    <t>22,951,685.8</t>
   </si>
   <si>
     <t>SHEL</t>
   </si>
   <si>
-    <t>13,532,890.0</t>
+    <t>17,222,910.2</t>
+  </si>
+  <si>
+    <t>19,239,356.8</t>
+  </si>
+  <si>
+    <t>15,938,534.5</t>
+  </si>
+  <si>
+    <t>UPCL</t>
+  </si>
+  <si>
+    <t>13,289,650.6</t>
+  </si>
+  <si>
+    <t>NRM</t>
+  </si>
+  <si>
+    <t>12,891,372.0</t>
+  </si>
+  <si>
+    <t>12,083,722.3</t>
+  </si>
+  <si>
+    <t>9,997,181.4</t>
+  </si>
+  <si>
+    <t>EBL</t>
+  </si>
+  <si>
+    <t>9,056,596.19</t>
   </si>
   <si>
     <t>SFCL</t>
   </si>
   <si>
-    <t>2,584,149,379.9</t>
+    <t>8,534,380.6</t>
+  </si>
+  <si>
+    <t>8,391,060.69</t>
+  </si>
+  <si>
+    <t>MANDU</t>
+  </si>
+  <si>
+    <t>8,202,477.0</t>
+  </si>
+  <si>
+    <t>30,275,887.6</t>
+  </si>
+  <si>
+    <t>20,278,224.8</t>
   </si>
   <si>
     <t>IGI</t>
   </si>
   <si>
-    <t>30,531,577.0</t>
-  </si>
-  <si>
-    <t>JFL</t>
-  </si>
-  <si>
-    <t>9,524,003.9</t>
-  </si>
-  <si>
-    <t>CITY</t>
-  </si>
-  <si>
-    <t>7,831,901.5</t>
-  </si>
-  <si>
-    <t>ICFC</t>
-  </si>
-  <si>
-    <t>5,652,714.4</t>
-  </si>
-  <si>
-    <t>SHIVM</t>
-  </si>
-  <si>
-    <t>720,399,821.7</t>
-  </si>
-  <si>
-    <t>UMRH</t>
-  </si>
-  <si>
-    <t>27,812,265.0</t>
-  </si>
-  <si>
-    <t>ALICL</t>
-  </si>
-  <si>
-    <t>21,786,808.5</t>
-  </si>
-  <si>
-    <t>NABIL</t>
-  </si>
-  <si>
-    <t>20,480,429.89</t>
-  </si>
-  <si>
-    <t>HLBSL</t>
-  </si>
-  <si>
-    <t>15,009,450.0</t>
-  </si>
-  <si>
-    <t>GMFBS</t>
-  </si>
-  <si>
-    <t>237,288,742.4</t>
-  </si>
-  <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>58,638,310.3</t>
-  </si>
-  <si>
-    <t>RHPL</t>
-  </si>
-  <si>
-    <t>53,848,911.7</t>
-  </si>
-  <si>
-    <t>PROFL</t>
-  </si>
-  <si>
-    <t>44,357,925.9</t>
-  </si>
-  <si>
-    <t>37,232,075.29</t>
-  </si>
-  <si>
-    <t>MAKAR</t>
-  </si>
-  <si>
-    <t>119,460,583.0</t>
-  </si>
-  <si>
-    <t>56,339,683.0</t>
-  </si>
-  <si>
-    <t>MMKJL</t>
-  </si>
-  <si>
-    <t>55,124,955.0</t>
-  </si>
-  <si>
-    <t>GBIME</t>
-  </si>
-  <si>
-    <t>26,736,339.5</t>
-  </si>
-  <si>
-    <t>17,481,580.0</t>
-  </si>
-  <si>
-    <t>147,521,748.0</t>
-  </si>
-  <si>
-    <t>PRVU</t>
-  </si>
-  <si>
-    <t>46,126,529.5</t>
-  </si>
-  <si>
-    <t>18,041,594.0</t>
-  </si>
-  <si>
-    <t>STC</t>
-  </si>
-  <si>
-    <t>16,652,644.0</t>
-  </si>
-  <si>
-    <t>5,050,561.5</t>
-  </si>
-  <si>
-    <t>EDBL</t>
-  </si>
-  <si>
-    <t>176,991,340.0</t>
-  </si>
-  <si>
-    <t>BNL</t>
-  </si>
-  <si>
-    <t>88,369,050.0</t>
-  </si>
-  <si>
-    <t>EBL</t>
-  </si>
-  <si>
-    <t>73,234,387.5</t>
-  </si>
-  <si>
-    <t>UMHL</t>
-  </si>
-  <si>
-    <t>29,600,600.0</t>
-  </si>
-  <si>
-    <t>NTC</t>
-  </si>
-  <si>
-    <t>24,642,296.2</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>2,959,531,081.4</t>
-  </si>
-  <si>
-    <t>PCBL</t>
-  </si>
-  <si>
-    <t>188,356,230.0</t>
-  </si>
-  <si>
-    <t>NFS</t>
-  </si>
-  <si>
-    <t>30,021,422.0</t>
-  </si>
-  <si>
-    <t>18,256,657.89</t>
-  </si>
-  <si>
-    <t>HDHPC</t>
-  </si>
-  <si>
-    <t>11,922,456.7</t>
-  </si>
-  <si>
-    <t>65,193,748.0</t>
+    <t>12,509,030.1</t>
+  </si>
+  <si>
+    <t>6,931,501.9</t>
+  </si>
+  <si>
+    <t>6,892,910.8</t>
+  </si>
+  <si>
+    <t>36,637,508.29</t>
+  </si>
+  <si>
+    <t>35,276,907.4</t>
+  </si>
+  <si>
+    <t>29,337,668.3</t>
+  </si>
+  <si>
+    <t>22,280,427.7</t>
+  </si>
+  <si>
+    <t>14,901,325.9</t>
+  </si>
+  <si>
+    <t>95,769,414.1</t>
+  </si>
+  <si>
+    <t>NIMB</t>
+  </si>
+  <si>
+    <t>36,021,999.1</t>
+  </si>
+  <si>
+    <t>22,214,076.1</t>
+  </si>
+  <si>
+    <t>CHDC</t>
+  </si>
+  <si>
+    <t>19,086,998.0</t>
   </si>
   <si>
     <t>LBBL</t>
   </si>
   <si>
-    <t>34,458,415.0</t>
-  </si>
-  <si>
-    <t>UPPER</t>
-  </si>
-  <si>
-    <t>12,571,144.5</t>
-  </si>
-  <si>
-    <t>10,829,150.0</t>
-  </si>
-  <si>
-    <t>GHL</t>
-  </si>
-  <si>
-    <t>4,617,134.3</t>
-  </si>
-  <si>
-    <t>438,063,958.6</t>
-  </si>
-  <si>
-    <t>247,784,510.0</t>
-  </si>
-  <si>
-    <t>120,684,776.0</t>
-  </si>
-  <si>
-    <t>9,128,930.0</t>
-  </si>
-  <si>
-    <t>NBL</t>
-  </si>
-  <si>
-    <t>6,404,096.9</t>
-  </si>
-  <si>
-    <t>CYCL</t>
-  </si>
-  <si>
-    <t>104,710,947.2</t>
-  </si>
-  <si>
-    <t>63,084,092.5</t>
-  </si>
-  <si>
-    <t>61,217,143.5</t>
-  </si>
-  <si>
-    <t>58,156,363.0</t>
-  </si>
-  <si>
-    <t>NLIC</t>
-  </si>
-  <si>
-    <t>42,853,227.5</t>
-  </si>
-  <si>
-    <t>251,442,043.6</t>
-  </si>
-  <si>
-    <t>118,104,513.19</t>
-  </si>
-  <si>
-    <t>114,718,500.0</t>
-  </si>
-  <si>
-    <t>91,763,777.4</t>
-  </si>
-  <si>
-    <t>29,853,165.0</t>
-  </si>
-  <si>
-    <t>478,201,121.0</t>
-  </si>
-  <si>
-    <t>AHPC</t>
-  </si>
-  <si>
-    <t>80,366,284.39</t>
-  </si>
-  <si>
-    <t>HDL</t>
-  </si>
-  <si>
-    <t>53,702,900.0</t>
-  </si>
-  <si>
-    <t>17,841,935.3</t>
-  </si>
-  <si>
-    <t>FMDBL</t>
-  </si>
-  <si>
-    <t>10,911,274.5</t>
-  </si>
-  <si>
-    <t>144,220,047.0</t>
-  </si>
-  <si>
-    <t>79,281,711.3</t>
-  </si>
-  <si>
-    <t>28,293,114.5</t>
-  </si>
-  <si>
-    <t>26,721,094.6</t>
-  </si>
-  <si>
-    <t>SCB</t>
-  </si>
-  <si>
-    <t>18,103,904.5</t>
+    <t>12,718,359.8</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -530,109 +548,109 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>4,798,304,771.7</t>
-  </si>
-  <si>
-    <t>2,914,522,880.2</t>
-  </si>
-  <si>
-    <t>797,066,054.5</t>
-  </si>
-  <si>
-    <t>589,491,679.79</t>
-  </si>
-  <si>
-    <t>463,166,469.8</t>
+    <t>246,923,792.7</t>
+  </si>
+  <si>
+    <t>242,612,709.0</t>
+  </si>
+  <si>
+    <t>230,264,677.5</t>
+  </si>
+  <si>
+    <t>215,604,912.8</t>
+  </si>
+  <si>
+    <t>201,980,940.9</t>
+  </si>
+  <si>
+    <t>Hydro Power</t>
+  </si>
+  <si>
+    <t>4,378,536,254.5</t>
+  </si>
+  <si>
+    <t>Promoter Shares/debenture</t>
+  </si>
+  <si>
+    <t>3,265,069,125.65</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>6,118,862,226.5</t>
+    <t>1,236,152,955.5</t>
+  </si>
+  <si>
+    <t>Microfinance</t>
+  </si>
+  <si>
+    <t>1,056,694,150.4</t>
+  </si>
+  <si>
+    <t>Development Banks</t>
+  </si>
+  <si>
+    <t>989,116,691.4</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>3,827,093,202.3</t>
-  </si>
-  <si>
-    <t>Hydro Power</t>
-  </si>
-  <si>
-    <t>2,721,633,138.1</t>
-  </si>
-  <si>
-    <t>Promoter Shares/debenture</t>
-  </si>
-  <si>
-    <t>1,722,914,696.8</t>
+    <t>984,708,224.5</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t>530,108,441.5</t>
   </si>
   <si>
     <t>Manufacturing And Processing</t>
   </si>
   <si>
-    <t>1,300,610,746.1</t>
-  </si>
-  <si>
-    <t>Microfinance</t>
-  </si>
-  <si>
-    <t>1,129,557,531.3</t>
+    <t>431,789,745.7</t>
+  </si>
+  <si>
+    <t>Non Life Insurance</t>
+  </si>
+  <si>
+    <t>423,292,089.4</t>
   </si>
   <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>818,226,265.2</t>
-  </si>
-  <si>
-    <t>Development Banks</t>
-  </si>
-  <si>
-    <t>758,065,901.8</t>
+    <t>328,837,909.8</t>
+  </si>
+  <si>
+    <t>Hotels And Tourism</t>
+  </si>
+  <si>
+    <t>241,685,745.2</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>488,690,219.1</t>
-  </si>
-  <si>
-    <t>Hotels And Tourism</t>
-  </si>
-  <si>
-    <t>410,366,846.8</t>
-  </si>
-  <si>
-    <t>Investment</t>
-  </si>
-  <si>
-    <t>229,379,602.5</t>
-  </si>
-  <si>
-    <t>Non Life Insurance</t>
-  </si>
-  <si>
-    <t>145,889,732.19</t>
+    <t>136,274,015.3</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>30,848,228.8</t>
+    <t>58,175,374.3</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>10,975,861.27</t>
+    <t>50,678,021.61</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>1,726,391.0</t>
+    <t>5,212,251.0</t>
   </si>
   <si>
     <t>Total</t>
@@ -644,214 +662,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>4,813,084,436.8</t>
-  </si>
-  <si>
-    <t>46,050,090.6</t>
-  </si>
-  <si>
-    <t>35,619,575.0</t>
-  </si>
-  <si>
-    <t>29,245,122.5</t>
-  </si>
-  <si>
-    <t>16,345,326.7</t>
-  </si>
-  <si>
-    <t>2,604,762,335.1</t>
-  </si>
-  <si>
-    <t>31,784,828.8</t>
-  </si>
-  <si>
-    <t>20,752,922.1</t>
-  </si>
-  <si>
-    <t>15,044,414.8</t>
-  </si>
-  <si>
-    <t>4,595,467.0</t>
-  </si>
-  <si>
-    <t>720,980,112.7</t>
-  </si>
-  <si>
-    <t>67,535,509.9</t>
-  </si>
-  <si>
-    <t>33,269,290.0</t>
-  </si>
-  <si>
-    <t>31,761,531.1</t>
-  </si>
-  <si>
-    <t>23,772,574.5</t>
-  </si>
-  <si>
-    <t>252,555,038.2</t>
-  </si>
-  <si>
-    <t>235,951,400.4</t>
-  </si>
-  <si>
-    <t>151,288,897.19</t>
-  </si>
-  <si>
-    <t>53,762,602.2</t>
-  </si>
-  <si>
-    <t>31,170,223.4</t>
-  </si>
-  <si>
-    <t>260,848,625.4</t>
-  </si>
-  <si>
-    <t>135,696,584.9</t>
-  </si>
-  <si>
-    <t>35,242,420.6</t>
-  </si>
-  <si>
-    <t>15,303,559.6</t>
-  </si>
-  <si>
-    <t>14,437,896.5</t>
-  </si>
-  <si>
-    <t>147,807,396.0</t>
-  </si>
-  <si>
-    <t>51,285,884.8</t>
-  </si>
-  <si>
-    <t>43,667,022.6</t>
-  </si>
-  <si>
-    <t>37,914,433.1</t>
-  </si>
-  <si>
-    <t>34,696,072.9</t>
-  </si>
-  <si>
-    <t>181,536,563.8</t>
-  </si>
-  <si>
-    <t>93,867,037.6</t>
-  </si>
-  <si>
-    <t>83,575,631.5</t>
-  </si>
-  <si>
-    <t>63,724,333.6</t>
-  </si>
-  <si>
-    <t>61,119,033.8</t>
-  </si>
-  <si>
-    <t>3,159,318,141.9</t>
-  </si>
-  <si>
-    <t>62,920,615.6</t>
-  </si>
-  <si>
-    <t>33,967,179.7</t>
-  </si>
-  <si>
-    <t>29,280,717.0</t>
-  </si>
-  <si>
-    <t>7,955,733.1</t>
-  </si>
-  <si>
-    <t>83,685,064.8</t>
-  </si>
-  <si>
-    <t>37,970,611.5</t>
-  </si>
-  <si>
-    <t>29,262,374.7</t>
-  </si>
-  <si>
-    <t>12,890,457.8</t>
-  </si>
-  <si>
-    <t>11,567,068.3</t>
-  </si>
-  <si>
-    <t>438,599,957.6</t>
-  </si>
-  <si>
-    <t>250,724,033.5</t>
-  </si>
-  <si>
-    <t>125,761,041.7</t>
-  </si>
-  <si>
-    <t>32,617,628.7</t>
-  </si>
-  <si>
-    <t>23,419,657.5</t>
-  </si>
-  <si>
-    <t>171,928,291.9</t>
-  </si>
-  <si>
-    <t>106,109,128.2</t>
-  </si>
-  <si>
-    <t>105,474,534.1</t>
-  </si>
-  <si>
-    <t>78,569,130.7</t>
-  </si>
-  <si>
-    <t>61,746,269.5</t>
-  </si>
-  <si>
-    <t>260,586,775.1</t>
-  </si>
-  <si>
-    <t>143,752,729.5</t>
-  </si>
-  <si>
-    <t>124,596,465.5</t>
-  </si>
-  <si>
-    <t>92,832,342.4</t>
-  </si>
-  <si>
-    <t>71,064,196.2</t>
-  </si>
-  <si>
-    <t>487,448,016.5</t>
-  </si>
-  <si>
-    <t>115,510,009.9</t>
-  </si>
-  <si>
-    <t>55,680,800.8</t>
-  </si>
-  <si>
-    <t>36,704,823.6</t>
-  </si>
-  <si>
-    <t>21,961,714.3</t>
-  </si>
-  <si>
-    <t>150,967,115.3</t>
-  </si>
-  <si>
-    <t>132,372,883.4</t>
-  </si>
-  <si>
-    <t>66,255,672.5</t>
-  </si>
-  <si>
-    <t>37,437,309.79</t>
-  </si>
-  <si>
-    <t>29,954,784.5</t>
+    <t>334,986,895.8</t>
+  </si>
+  <si>
+    <t>168,703,181.69</t>
+  </si>
+  <si>
+    <t>107,503,062.9</t>
+  </si>
+  <si>
+    <t>75,629,403.4</t>
+  </si>
+  <si>
+    <t>49,522,590.0</t>
+  </si>
+  <si>
+    <t>179,013,919.0</t>
+  </si>
+  <si>
+    <t>149,082,300.1</t>
+  </si>
+  <si>
+    <t>42,637,747.2</t>
+  </si>
+  <si>
+    <t>35,913,502.7</t>
+  </si>
+  <si>
+    <t>32,606,525.1</t>
+  </si>
+  <si>
+    <t>159,683,468.5</t>
+  </si>
+  <si>
+    <t>158,621,482.1</t>
+  </si>
+  <si>
+    <t>63,426,073.7</t>
+  </si>
+  <si>
+    <t>57,032,685.9</t>
+  </si>
+  <si>
+    <t>43,964,785.5</t>
+  </si>
+  <si>
+    <t>207,010,552.5</t>
+  </si>
+  <si>
+    <t>178,370,000.6</t>
+  </si>
+  <si>
+    <t>36,076,105.2</t>
+  </si>
+  <si>
+    <t>26,372,229.2</t>
+  </si>
+  <si>
+    <t>25,645,215.3</t>
+  </si>
+  <si>
+    <t>127,241,134.0</t>
+  </si>
+  <si>
+    <t>116,646,145.5</t>
+  </si>
+  <si>
+    <t>68,466,735.8</t>
+  </si>
+  <si>
+    <t>37,432,560.4</t>
+  </si>
+  <si>
+    <t>33,000,387.1</t>
+  </si>
+  <si>
+    <t>134,053,850.9</t>
+  </si>
+  <si>
+    <t>91,967,413.8</t>
+  </si>
+  <si>
+    <t>91,378,266.5</t>
+  </si>
+  <si>
+    <t>40,284,990.6</t>
+  </si>
+  <si>
+    <t>30,849,171.9</t>
+  </si>
+  <si>
+    <t>92,081,770.3</t>
+  </si>
+  <si>
+    <t>62,132,478.1</t>
+  </si>
+  <si>
+    <t>31,151,014.3</t>
+  </si>
+  <si>
+    <t>26,391,673.2</t>
+  </si>
+  <si>
+    <t>20,025,913.6</t>
+  </si>
+  <si>
+    <t>227,038,712.1</t>
+  </si>
+  <si>
+    <t>141,988,163.1</t>
+  </si>
+  <si>
+    <t>90,020,702.4</t>
+  </si>
+  <si>
+    <t>63,220,507.0</t>
+  </si>
+  <si>
+    <t>50,826,063.0</t>
+  </si>
+  <si>
+    <t>211,583,845.2</t>
+  </si>
+  <si>
+    <t>138,096,256.0</t>
+  </si>
+  <si>
+    <t>64,373,829.1</t>
+  </si>
+  <si>
+    <t>46,969,259.7</t>
+  </si>
+  <si>
+    <t>41,507,057.5</t>
+  </si>
+  <si>
+    <t>139,045,448.0</t>
+  </si>
+  <si>
+    <t>128,009,433.2</t>
+  </si>
+  <si>
+    <t>42,141,227.2</t>
+  </si>
+  <si>
+    <t>39,388,337.29</t>
+  </si>
+  <si>
+    <t>38,103,958.1</t>
+  </si>
+  <si>
+    <t>129,500,516.0</t>
+  </si>
+  <si>
+    <t>96,303,864.9</t>
+  </si>
+  <si>
+    <t>44,082,944.8</t>
+  </si>
+  <si>
+    <t>27,408,390.7</t>
+  </si>
+  <si>
+    <t>25,565,149.7</t>
+  </si>
+  <si>
+    <t>182,180,882.5</t>
+  </si>
+  <si>
+    <t>104,582,186.2</t>
+  </si>
+  <si>
+    <t>37,939,971.1</t>
+  </si>
+  <si>
+    <t>32,051,378.0</t>
+  </si>
+  <si>
+    <t>30,887,731.5</t>
+  </si>
+  <si>
+    <t>155,294,528.3</t>
+  </si>
+  <si>
+    <t>67,593,589.8</t>
+  </si>
+  <si>
+    <t>60,452,950.0</t>
+  </si>
+  <si>
+    <t>39,547,180.5</t>
+  </si>
+  <si>
+    <t>35,899,754.9</t>
+  </si>
+  <si>
+    <t>206,689,505.6</t>
+  </si>
+  <si>
+    <t>101,267,253.3</t>
+  </si>
+  <si>
+    <t>50,424,468.0</t>
+  </si>
+  <si>
+    <t>39,712,255.79</t>
+  </si>
+  <si>
+    <t>26,075,734.4</t>
   </si>
 </sst>
 </file>
@@ -1438,27 +1456,27 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="4" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
       <c r="T4" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
@@ -1468,37 +1486,37 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
       <c r="T5" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U5" s="6"/>
       <c r="V5" s="6"/>
@@ -1508,37 +1526,37 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
       <c r="N6" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
       <c r="T6" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U6" s="7"/>
       <c r="V6" s="7"/>
@@ -1548,1070 +1566,1070 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
       <c r="N7" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R7" s="8"/>
       <c r="S7" s="8"/>
       <c r="T7" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U7" s="8"/>
       <c r="V7" s="8"/>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="I8" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="L8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="K8" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="L8" s="5" t="s">
+      <c r="M8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="N8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="M8" s="5" t="s">
+      <c r="O8" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="N8" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="O8" s="6" t="s">
+      <c r="P8" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="P8" s="6" t="s">
+      <c r="R8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="Q8" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="R8" s="5" t="s">
+      <c r="S8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="T8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="S8" s="5" t="s">
+      <c r="U8" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="T8" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="U8" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="V8" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.5766945576223399</v>
+        <v>0.04494627477768246</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.8961417382379595</v>
+        <v>0.02525001170676074</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J9" s="14">
-        <v>0.3945773486821137</v>
+        <v>0.02001352801225427</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1575989227350069</v>
+        <v>0.0978360020436027</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="P9" s="18">
-        <v>0.0937142804653792</v>
+        <v>0.03125346357283073</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>55</v>
+        <v>103</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1282184278166824</v>
+        <v>0.08510114574216859</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1700263149994863</v>
+        <v>0.009893560211022978</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C10" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0.04086843847184603</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G10" s="12">
+        <v>0.01482514370416639</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="J10" s="14">
+        <v>0.01608879240078276</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="M10" s="16">
+        <v>0.02275959448859526</v>
+      </c>
+      <c r="N10" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="10">
-        <v>0.004273039509842923</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10" s="12">
-        <v>0.01058786333976749</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="J10" s="14">
-        <v>0.01523333217746734</v>
-      </c>
-      <c r="K10" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="L10" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="M10" s="16">
-        <v>0.03894552451503515</v>
-      </c>
-      <c r="N10" s="17" t="s">
-        <v>75</v>
-      </c>
       <c r="O10" s="17" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="P10" s="18">
-        <v>0.04419728015217</v>
+        <v>0.01670247935953616</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="S10" s="16">
-        <v>0.04009084201693312</v>
+        <v>0.03860409880950395</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="V10" s="18">
-        <v>0.08489152029418705</v>
+        <v>0.00966830585357382</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.002919335318478482</v>
+        <v>0.02968544856687661</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G11" s="12">
-        <v>0.003302772462117257</v>
+        <v>0.01388114642241113</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J11" s="14">
-        <v>0.01193306949172852</v>
+        <v>0.01587320578139381</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M11" s="16">
-        <v>0.03576457268278948</v>
+        <v>0.02019517835476708</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P11" s="18">
-        <v>0.04324435193415562</v>
+        <v>0.01103351802814447</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="S11" s="16">
-        <v>0.01568083926165849</v>
+        <v>0.02389934532941311</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="V11" s="18">
-        <v>0.07035244231649665</v>
+        <v>0.008558127967345211</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.001871220553904161</v>
+        <v>0.02767572766854908</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G12" s="12">
-        <v>0.002715978371261989</v>
+        <v>0.01228675796024816</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J12" s="14">
-        <v>0.01121753988048202</v>
+        <v>0.01305717433829806</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M12" s="16">
-        <v>0.02946099029348331</v>
+        <v>0.01574629730551711</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="P12" s="18">
-        <v>0.02097408831932954</v>
+        <v>0.009711790741605447</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="S12" s="16">
-        <v>0.01447363430557309</v>
+        <v>0.02270870574042853</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="V12" s="18">
-        <v>0.02843574685503706</v>
+        <v>0.008540251509120413</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.00163269000140065</v>
+        <v>0.02138078037349774</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G13" s="12">
-        <v>0.001960271084783331</v>
+        <v>0.01025392987386376</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J13" s="14">
-        <v>0.008220975086030828</v>
+        <v>0.01185980122808844</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M13" s="16">
-        <v>0.02472824837419956</v>
+        <v>0.0156181861602269</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="P13" s="18">
-        <v>0.01371392680293519</v>
+        <v>0.008999837017944708</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="S13" s="16">
-        <v>0.004389692122692751</v>
+        <v>0.01902063855910693</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="V13" s="18">
-        <v>0.02367256395715093</v>
+        <v>0.008436910637371273</v>
       </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S15" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="V15" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D16" s="10">
-        <v>0.3570557955792321</v>
+        <v>0.02467824700951957</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G16" s="12">
-        <v>0.02260815071659221</v>
+        <v>0.02471438557270934</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="J16" s="14">
-        <v>0.2399363660719507</v>
+        <v>0.01686068154029289</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>140</v>
+        <v>58</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M16" s="16">
-        <v>0.06954536616601913</v>
+        <v>0.01024679802215017</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="P16" s="18">
-        <v>0.1972509224630061</v>
+        <v>0.03159615222881765</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="S16" s="16">
-        <v>0.4156281819192862</v>
+        <v>0.04091290908388732</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="V16" s="18">
-        <v>0.1385446493622949</v>
+        <v>0.1135975907458764</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D17" s="10">
-        <v>0.02272443900914891</v>
+        <v>0.01250698399099105</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G17" s="12">
-        <v>0.01194962804983818</v>
+        <v>0.02372301415974684</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="J17" s="14">
-        <v>0.1357165174882728</v>
+        <v>0.01396795938747138</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>53</v>
+        <v>146</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="M17" s="16">
-        <v>0.04189825829560943</v>
+        <v>0.009282727632567786</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="P17" s="18">
-        <v>0.09265047261867021</v>
+        <v>0.02116251342243011</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>153</v>
+        <v>103</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="S17" s="16">
-        <v>0.06985030190420714</v>
+        <v>0.03939353335382013</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>101</v>
+        <v>165</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="V17" s="18">
-        <v>0.07616178971915878</v>
+        <v>0.04272775760471241</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D18" s="10">
-        <v>0.003621966595991656</v>
+        <v>0.009085891580918447</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>129</v>
+        <v>80</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G18" s="12">
-        <v>0.004359472161902076</v>
+        <v>0.02120908726336412</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="J18" s="14">
-        <v>0.06610145853173909</v>
+        <v>0.01164657264157408</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>55</v>
+        <v>148</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="M18" s="16">
-        <v>0.04065829575787887</v>
+        <v>0.008747472987972064</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="P18" s="18">
-        <v>0.08999421745302888</v>
+        <v>0.01305452129087909</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="S18" s="16">
-        <v>0.04667583932910361</v>
+        <v>0.03276121689452181</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="V18" s="18">
-        <v>0.0271797139808848</v>
+        <v>0.02634938878262965</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D19" s="10">
-        <v>0.002202594036626485</v>
+        <v>0.00868624539334082</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G19" s="12">
-        <v>0.003755376287502055</v>
+        <v>0.01924146904946747</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="J19" s="14">
-        <v>0.005000097011690595</v>
+        <v>0.01129753557610869</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="M19" s="16">
-        <v>0.03862543189485088</v>
+        <v>0.008600574576400302</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="P19" s="18">
-        <v>0.0719867269677248</v>
+        <v>0.00723376939762251</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>145</v>
+        <v>109</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="S19" s="16">
-        <v>0.01550730603716116</v>
+        <v>0.02488043415442159</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>53</v>
+        <v>168</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="V19" s="18">
-        <v>0.02566955675679202</v>
+        <v>0.02264018223090874</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D20" s="10">
-        <v>0.001438397551906665</v>
+        <v>0.007852658101497826</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G20" s="12">
-        <v>0.001601148443454232</v>
+        <v>0.01443876917986816</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="J20" s="14">
-        <v>0.003507651583730734</v>
+        <v>0.01058974037643688</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="M20" s="16">
-        <v>0.02846162199441188</v>
+        <v>0.008407282186590335</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="P20" s="18">
-        <v>0.02341917147339924</v>
+        <v>0.007193495424935494</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>158</v>
+        <v>97</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="S20" s="16">
-        <v>0.009483526875415394</v>
+        <v>0.01664023073796412</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="V20" s="18">
-        <v>0.01739147332992461</v>
+        <v>0.01508597546614004</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D31" s="22">
-        <v>0.4334598153258003</v>
+        <v>0.3101752329139309</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D32" s="22">
-        <v>0.2711110417749138</v>
+        <v>0.2312972915292721</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D33" s="22">
-        <v>0.1928003203465173</v>
+        <v>0.08756899762914971</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="D34" s="22">
-        <v>0.1220511687716516</v>
+        <v>0.07485614716156698</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D35" s="22">
-        <v>0.09213518346166956</v>
+        <v>0.07006896421577904</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D36" s="22">
-        <v>0.08001778448233293</v>
+        <v>0.06975666869782016</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D37" s="22">
-        <v>0.05796309717062908</v>
+        <v>0.03755284865870771</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D38" s="22">
-        <v>0.05370134081070312</v>
+        <v>0.03058795843124484</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D39" s="22">
-        <v>0.03461878438857686</v>
+        <v>0.02998598499334852</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D40" s="22">
-        <v>0.02907036162039969</v>
+        <v>0.0232948568504642</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="D41" s="22">
-        <v>0.01624923661600856</v>
+        <v>0.017121002990975</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="D42" s="22">
-        <v>0.01033481945441911</v>
+        <v>0.009653642673930743</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="D43" s="22">
-        <v>0.002185286588226474</v>
+        <v>0.004121139856912794</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="D44" s="22">
-        <v>0.0007775293221232007</v>
+        <v>0.003590027863842362</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D45" s="22">
-        <v>0.0001222974298717238</v>
+        <v>0.0003692355330549814</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -2774,27 +2792,27 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="4" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
       <c r="T4" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
@@ -2804,37 +2822,37 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
       <c r="T5" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U5" s="6"/>
       <c r="V5" s="6"/>
@@ -2844,37 +2862,37 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
       <c r="N6" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
       <c r="T6" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U6" s="7"/>
       <c r="V6" s="7"/>
@@ -2884,371 +2902,371 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
       <c r="N7" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R7" s="8"/>
       <c r="S7" s="8"/>
       <c r="T7" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U7" s="8"/>
       <c r="V7" s="8"/>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="I8" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="L8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="K8" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="L8" s="5" t="s">
+      <c r="M8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="N8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="M8" s="5" t="s">
+      <c r="O8" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="N8" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="O8" s="6" t="s">
+      <c r="P8" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="P8" s="6" t="s">
+      <c r="R8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="Q8" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="R8" s="5" t="s">
+      <c r="S8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="T8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="S8" s="5" t="s">
+      <c r="U8" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="T8" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="U8" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="V8" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="D9" s="10">
-        <v>0.5806797244240099</v>
+        <v>0.2135964228692023</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="G9" s="12">
-        <v>0.9032899819296085</v>
+        <v>0.1500757204450044</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>184</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="J9" s="14">
-        <v>0.3948951856350765</v>
+        <v>0.1399408586064525</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1677382649890875</v>
+        <v>0.2121793368600087</v>
       </c>
       <c r="N9" s="17" t="s">
         <v>182</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="P9" s="18">
-        <v>0.2046301853369009</v>
+        <v>0.1327898389882841</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1284666985833017</v>
+        <v>0.1496972165603491</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1743926735657414</v>
+        <v>0.1092234650905648</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="D10" s="10">
-        <v>0.005555762478392573</v>
+        <v>0.1075695694057447</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="G10" s="12">
-        <v>0.011022471050621</v>
+        <v>0.1249826478191668</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="J10" s="14">
-        <v>0.0369905455769724</v>
+        <v>0.1390101718544649</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="M10" s="16">
-        <v>0.1567107067311773</v>
+        <v>0.1828236676148543</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="P10" s="18">
-        <v>0.1064510778045738</v>
+        <v>0.1217328264266252</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="S10" s="16">
-        <v>0.04457509219754831</v>
+        <v>0.1026995179003383</v>
       </c>
       <c r="T10" s="17" t="s">
         <v>184</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="V10" s="18">
-        <v>0.09017314916676843</v>
+        <v>0.07369889317544573</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D11" s="10">
-        <v>0.004297361757661562</v>
+        <v>0.06854676995076313</v>
       </c>
       <c r="E11" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="G11" s="12">
+        <v>0.03574521280209484</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="J11" s="14">
+        <v>0.05558433377600473</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="M11" s="16">
+        <v>0.03697687864403874</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="O11" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="P11" s="18">
+        <v>0.07145241901832927</v>
+      </c>
+      <c r="Q11" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="G11" s="12">
-        <v>0.007196781977414418</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="J11" s="14">
-        <v>0.01822225359489752</v>
-      </c>
-      <c r="K11" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="L11" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="M11" s="16">
-        <v>0.1004808191881892</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>178</v>
-      </c>
-      <c r="O11" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="P11" s="18">
-        <v>0.02764692759273792</v>
-      </c>
-      <c r="Q11" s="15" t="s">
-        <v>180</v>
-      </c>
       <c r="R11" s="15" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="S11" s="16">
-        <v>0.03795316325297025</v>
+        <v>0.1020416202691853</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="V11" s="18">
-        <v>0.08028673407241277</v>
+        <v>0.03695000337033849</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D12" s="10">
-        <v>0.00352830911176306</v>
+        <v>0.04822328942567517</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="G12" s="12">
-        <v>0.00521716280587719</v>
+        <v>0.03010796490861758</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="J12" s="14">
-        <v>0.01739642397738047</v>
+        <v>0.04998139825274472</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="M12" s="16">
-        <v>0.03570724891730351</v>
+        <v>0.0270307094763981</v>
       </c>
       <c r="N12" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="O12" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="P12" s="18">
+        <v>0.03906491173235863</v>
+      </c>
+      <c r="Q12" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="O12" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="P12" s="18">
-        <v>0.01200531623450261</v>
-      </c>
-      <c r="Q12" s="15" t="s">
-        <v>178</v>
-      </c>
       <c r="R12" s="15" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="S12" s="16">
-        <v>0.03295330396737695</v>
+        <v>0.04498603301204999</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="V12" s="18">
-        <v>0.06121663137759142</v>
+        <v>0.03130467612699443</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -3257,462 +3275,462 @@
         <v>188</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="D13" s="10">
-        <v>0.001971999437867084</v>
+        <v>0.03157690109028477</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="G13" s="12">
-        <v>0.00159363456982295</v>
+        <v>0.02733557129482551</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>188</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="J13" s="14">
-        <v>0.01302071313041529</v>
+        <v>0.03852915952485409</v>
       </c>
       <c r="K13" s="15" t="s">
         <v>190</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="M13" s="16">
-        <v>0.02070217735390343</v>
+        <v>0.02628554298451113</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="P13" s="18">
-        <v>0.01132622198847897</v>
+        <v>0.03443946113809428</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="S13" s="16">
-        <v>0.03015606836932951</v>
+        <v>0.03444910486060297</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="V13" s="18">
-        <v>0.05871385624484821</v>
+        <v>0.02375388383466241</v>
       </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S15" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="V15" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D16" s="10">
-        <v>0.3811593193710886</v>
+        <v>0.1447658322322669</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="G16" s="12">
-        <v>0.02902064409191791</v>
+        <v>0.1773806091743865</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="J16" s="14">
-        <v>0.2402299434132348</v>
+        <v>0.1218544384163276</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="M16" s="16">
-        <v>0.114188786695301</v>
+        <v>0.1327339755199627</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="P16" s="18">
-        <v>0.204424769359196</v>
+        <v>0.190125388649228</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="S16" s="16">
-        <v>0.4236651149089574</v>
+        <v>0.1734165671294592</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="V16" s="18">
-        <v>0.1450262046751077</v>
+        <v>0.2451662682628474</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="D17" s="10">
-        <v>0.007591125027403148</v>
+        <v>0.09053537349722462</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="G17" s="12">
-        <v>0.01316760170918796</v>
+        <v>0.1157725344807281</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="J17" s="14">
-        <v>0.1373265531297055</v>
+        <v>0.1121828712765801</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="M17" s="16">
-        <v>0.07047398931585699</v>
+        <v>0.09870844720120182</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="P17" s="18">
-        <v>0.1127709514863726</v>
+        <v>0.109142784490908</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="S17" s="16">
-        <v>0.1003954472290243</v>
+        <v>0.07548139932160651</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="V17" s="18">
-        <v>0.1271636994802044</v>
+        <v>0.120118892910011</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="D18" s="10">
-        <v>0.004098006757756041</v>
+        <v>0.05739955878242153</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="G18" s="12">
-        <v>0.01014772425023017</v>
+        <v>0.05396758438647493</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="J18" s="14">
-        <v>0.06888183048739188</v>
+        <v>0.03693105850276286</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="M18" s="16">
-        <v>0.07005251400471306</v>
+        <v>0.04518363861910067</v>
       </c>
       <c r="N18" s="17" t="s">
         <v>186</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="P18" s="18">
-        <v>0.09774327078967918</v>
+        <v>0.03959444949295367</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="S18" s="16">
-        <v>0.04839493047594494</v>
+        <v>0.06750748514201731</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="V18" s="18">
-        <v>0.06364835614549166</v>
+        <v>0.05981135139305963</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="D19" s="10">
-        <v>0.003532603448320503</v>
+        <v>0.04031105191422048</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="G19" s="12">
-        <v>0.004470204915174867</v>
+        <v>0.03937652182368015</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="J19" s="14">
-        <v>0.0178653257053459</v>
+        <v>0.03451852463263947</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="M19" s="16">
-        <v>0.05218288163739689</v>
+        <v>0.02809274258193204</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="P19" s="18">
-        <v>0.07282499342843249</v>
+        <v>0.03344906784603656</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="S19" s="16">
-        <v>0.03190197268595719</v>
+        <v>0.04416212442920365</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="V19" s="18">
-        <v>0.03596406371514085</v>
+        <v>0.04710498257046301</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="D20" s="10">
+        <v>0.03240802963172125</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="G20" s="12">
+        <v>0.03479730287265943</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="J20" s="14">
+        <v>0.0333929408154</v>
+      </c>
+      <c r="K20" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="D20" s="10">
-        <v>0.0009598279366921774</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="G20" s="12">
-        <v>0.004011274570001958</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="J20" s="14">
-        <v>0.01282741345158384</v>
-      </c>
-      <c r="K20" s="15" t="s">
-        <v>194</v>
-      </c>
       <c r="L20" s="15" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="M20" s="16">
-        <v>0.04100972282832333</v>
+        <v>0.026203478250573</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="P20" s="18">
-        <v>0.05574834683113455</v>
+        <v>0.03223467729074427</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="S20" s="16">
-        <v>0.01908800917750209</v>
+        <v>0.04008906381762698</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="V20" s="18">
-        <v>0.02877599336294494</v>
+        <v>0.03092992300941068</v>
       </c>
     </row>
   </sheetData>
